--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf2a031ad0a18441f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra327fafda1704cee"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra327fafda1704cee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3703a1b44911456e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3703a1b44911456e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf9a7b5a78db04464"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf9a7b5a78db04464"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re82612539a5c495f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re82612539a5c495f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcebd47398a7549f5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcebd47398a7549f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdf705e3d85714e1e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdf705e3d85714e1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd986f43b51b1482b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd986f43b51b1482b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb93defa3ad604292"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb93defa3ad604292"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbe09e8f4222d454f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbe09e8f4222d454f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra064b6e672b2459b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra064b6e672b2459b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3fe65492b2ac4ea7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3fe65492b2ac4ea7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc3d3411981364944"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc3d3411981364944"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0b6f7ff787014fc6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0b6f7ff787014fc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2c4bd0f21e0d4d5b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2c4bd0f21e0d4d5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5c7fce111dfe4698"/>
   </x:sheets>
 </x:workbook>
 </file>
